--- a/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>role</t>
@@ -304,16 +304,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -350,7 +350,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -370,16 +370,16 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>RelatedPerson.meta.versionId</t>
   </si>
   <si>
-    <t>バージョン固有の識別子</t>
-  </si>
-  <si>
-    <t>URLのバージョン部分に表示されるバージョン固有の識別子。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi)</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
   </si>
   <si>
     <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。</t>
@@ -399,7 +399,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースのバージョンが最後に変更されたとき」</t>
+    <t>リソースのバージョンが最後に変更されたとき</t>
   </si>
   <si>
     <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。</t>
@@ -424,8 +424,8 @@
     <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。</t>
   </si>
   <si>
-    <t>「プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
-この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。」</t>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。</t>
   </si>
   <si>
     <t>Meta.source</t>
@@ -493,7 +493,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>「様々なタグを表すコードで、一般的にはワークフローに関連しています。</t>
+    <t>様々なタグを表すコードで、一般的にはワークフローに関連しています。例：「ジョーンズ博士によるレビューが必要です」。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/common-tags</t>
@@ -612,7 +612,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -640,13 +640,13 @@
 </t>
   </si>
   <si>
-    <t>この人の人間の識別子 / A human identifier for this person</t>
-  </si>
-  <si>
-    <t>特定の範囲内の人の識別子。 / Identifier for a person within a particular scope.</t>
-  </si>
-  <si>
-    <t>人々はさまざまなIDで知られています。一部の機関は、患者に関する他の組織と交換のためにいくつかの識別子を維持しています。例は、国民の識別子とローカル識別子です。 / People are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the patient. Examples are national person identifier and local identifier.</t>
+    <t>この人の人間のidentifier / A human identifier for this person</t>
+  </si>
+  <si>
+    <t>特定の範囲内の人のidentifier。 / Identifier for a person within a particular scope.</t>
+  </si>
+  <si>
+    <t>人々はさまざまなIDで知られています。一部の機関は、患者に関する他の組織と交換のためにいくつかのidentifierを維持しています。例は、国民のidentifierとローカルidentifierです。 / People are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the patient. Examples are national person identifier and local identifier.</t>
   </si>
   <si>
     <t>.id</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="305">
   <si>
     <t>Property</t>
   </si>
@@ -488,15 +488,6 @@
   </si>
   <si>
     <t>リソースの表示バージョンを変更することなく、タグを更新できます。タグのリストは集合です。ユニーク性はシステム/コードに基づき、バージョンと表示は無視されます。</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>様々なタグを表すコードで、一般的にはワークフローに関連しています。例：「ジョーンズ博士によるレビューが必要です」。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -2623,31 +2614,31 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2673,10 +2664,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2702,13 +2693,13 @@
         <v>128</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2758,7 +2749,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2784,10 +2775,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2810,16 +2801,16 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2845,31 +2836,31 @@
         <v>76</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2895,14 +2886,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2921,16 +2912,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2980,7 +2971,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2995,7 +2986,7 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
@@ -3006,14 +2997,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3032,16 +3023,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3091,7 +3082,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3106,7 +3097,7 @@
         <v>76</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3117,10 +3108,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3146,13 +3137,13 @@
         <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3202,7 +3193,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3214,10 +3205,10 @@
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3228,10 +3219,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3257,16 +3248,16 @@
         <v>106</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -3315,7 +3306,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3327,10 +3318,10 @@
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -3341,10 +3332,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3367,17 +3358,17 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3426,7 +3417,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3441,21 +3432,21 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3478,26 +3469,26 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="P20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N20" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q20" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="R20" t="s" s="2">
         <v>76</v>
       </c>
@@ -3541,7 +3532,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3556,10 +3547,10 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>76</v>
@@ -3567,10 +3558,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3593,17 +3584,17 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3652,7 +3643,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>85</v>
@@ -3667,21 +3658,21 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3704,17 +3695,17 @@
         <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -3739,13 +3730,13 @@
         <v>76</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>76</v>
@@ -3763,7 +3754,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3778,21 +3769,21 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3815,17 +3806,17 @@
         <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -3874,7 +3865,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3889,21 +3880,21 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3926,19 +3917,19 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -3987,7 +3978,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4002,21 +3993,21 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4039,17 +4030,17 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4074,13 +4065,13 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4098,7 +4089,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4113,21 +4104,21 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4150,13 +4141,13 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4207,7 +4198,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4222,7 +4213,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
@@ -4233,10 +4224,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4259,17 +4250,17 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4318,7 +4309,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4333,21 +4324,21 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4370,17 +4361,17 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4429,7 +4420,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4444,21 +4435,21 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4481,13 +4472,13 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4538,7 +4529,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4553,10 +4544,10 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>76</v>
@@ -4564,10 +4555,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4590,19 +4581,19 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -4651,7 +4642,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4666,7 +4657,7 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
@@ -4677,10 +4668,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4706,10 +4697,10 @@
         <v>99</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4786,10 +4777,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4815,13 +4806,13 @@
         <v>106</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4883,7 +4874,7 @@
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>103</v>
@@ -4897,14 +4888,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4926,16 +4917,16 @@
         <v>106</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -4984,7 +4975,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -4996,10 +4987,10 @@
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -5010,10 +5001,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5036,19 +5027,19 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -5073,13 +5064,13 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>76</v>
@@ -5097,7 +5088,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>85</v>
@@ -5112,7 +5103,7 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5123,10 +5114,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5149,19 +5140,19 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5210,7 +5201,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5225,7 +5216,7 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
@@ -418,7 +418,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースがどこから来たかを特定する」</t>
+    <t>リソースがどこから来たかを特定する</t>
   </si>
   <si>
     <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>role</t>
@@ -370,7 +370,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>RelatedPerson.meta.versionId</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
@@ -1288,17 +1288,17 @@
   <dimension ref="A1:AM35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.27734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.27734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.671875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="28.6484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="24.5625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1307,25 +1307,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="85.1171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.61328125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="22.28515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.27734375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="72.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="46.8203125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.81640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="89.0078125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="28.1484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="76.30859375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="24.1328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
@@ -434,7 +434,7 @@
     <t>RelatedPerson.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -472,7 +472,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -530,7 +530,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -680,7 +680,7 @@
     <t>RelatedPerson.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -715,7 +715,7 @@
     <t>患者は、この人に起因する情報の解釈に影響を与えるため、患者との関係を知る必要があります。 / We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
+    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype|4.0.1</t>
   </si>
   <si>
     <t>code</t>
@@ -1298,7 +1298,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="24.5625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="29.08984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1313,7 +1313,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="72.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="46.8203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-relatedperson.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -2107,7 +2107,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -5227,12 +5227,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AM35">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
